--- a/Dianguc.xlsx
+++ b/Dianguc.xlsx
@@ -1,43 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tool\Xola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\.tool\Xola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039FB905-0C3D-42B2-B6A8-814D369B57F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B315D493-6ECD-4D98-9710-2AB28899EDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
+    <workbookView xWindow="17160" yWindow="0" windowWidth="5976" windowHeight="13776" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
   <si>
     <t>Tầng</t>
   </si>
@@ -65,7 +53,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -127,14 +115,14 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,13 +438,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CB08FB-80B1-4D9C-AAE4-0416F8953E35}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="b">
+      <c r="B1" s="2" t="b">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="b">
@@ -465,120 +453,130 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="C12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -586,11 +584,11 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -599,7 +597,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -608,7 +606,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -617,7 +615,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -626,7 +624,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -635,7 +633,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -644,7 +642,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -653,7 +651,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -662,7 +660,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -671,7 +669,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -680,7 +678,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -689,7 +687,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -698,7 +696,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -707,7 +705,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -716,7 +714,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -725,7 +723,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -734,7 +732,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -743,7 +741,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -752,28 +750,28 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="1">
         <f>COUNTIF(B2:B31, "Up") / COUNTA(A2:A31)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="C33" s="1">
         <f>COUNTIF(B1:B100, "Dow") / COUNTA(A2:A31)</f>
@@ -781,11 +779,11 @@
       </c>
       <c r="D33" s="1">
         <f>COUNTIF(B2:B31, "Left") / COUNTA(A2:A31)</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E33" s="1">
         <f>COUNTIF(B2:B31, "Right") / COUNTA(A2:A31)</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.13333333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/Dianguc.xlsx
+++ b/Dianguc.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\.tool\Xola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B315D493-6ECD-4D98-9710-2AB28899EDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C8796D-2E74-4FC4-BC74-7EA038346AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17160" yWindow="0" windowWidth="5976" windowHeight="13776" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
+    <workbookView xWindow="17232" yWindow="0" windowWidth="5904" windowHeight="13776" activeTab="1" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="6">
   <si>
     <t>Tầng</t>
   </si>
@@ -58,7 +59,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -68,6 +69,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -112,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -123,6 +130,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -794,4 +803,375 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064059B2-0CFC-4C91-B4E1-43670BB0799C}">
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="1">
+        <f>COUNTIF(B2:B31, "Up") / COUNTA(A2:A31)</f>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="C33" s="1">
+        <f>COUNTIF(B1:B100, "Dow") / COUNTA(A2:A31)</f>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="D33" s="1">
+        <f>COUNTIF(B2:B31, "Left") / COUNTA(A2:A31)</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E33" s="1">
+        <f>COUNTIF(B2:B31, "Right") / COUNTA(A2:A31)</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A32:A33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Dianguc.xlsx
+++ b/Dianguc.xlsx
@@ -1,32 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\.tool\Xola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tool\Xola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C8796D-2E74-4FC4-BC74-7EA038346AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E0DC27-17EB-4E91-BFC4-A2089FFD7F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17232" yWindow="0" windowWidth="5904" windowHeight="13776" activeTab="1" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
+    <workbookView xWindow="21960" yWindow="615" windowWidth="6885" windowHeight="14865" activeTab="2" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="T3" sheetId="1" r:id="rId1"/>
+    <sheet name="T4" sheetId="2" r:id="rId2"/>
+    <sheet name="T5" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="6">
   <si>
     <t>Tầng</t>
   </si>
@@ -54,12 +67,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -78,8 +91,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -115,23 +134,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,22 +487,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CB08FB-80B1-4D9C-AAE4-0416F8953E35}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="b">
+      <c r="C1" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -473,7 +513,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -484,7 +524,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -495,7 +535,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -506,7 +546,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -517,7 +557,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -528,7 +568,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -539,7 +579,7 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -550,7 +590,7 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -561,7 +601,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -572,7 +612,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -585,7 +625,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -593,11 +633,11 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -606,7 +646,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -615,7 +655,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -624,7 +664,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -633,7 +673,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -642,7 +682,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -651,7 +691,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -660,7 +700,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -669,7 +709,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -678,7 +718,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -687,7 +727,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -696,7 +736,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -705,7 +745,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -714,7 +754,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -723,7 +763,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -732,7 +772,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -741,7 +781,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -750,7 +790,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -759,8 +799,8 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -776,8 +816,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="8"/>
       <c r="B33" s="1">
         <f>COUNTIF(B2:B31, "Up") / COUNTA(A2:A31)</f>
         <v>6.6666666666666666E-2</v>
@@ -807,67 +847,67 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064059B2-0CFC-4C91-B4E1-43670BB0799C}">
-  <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="b">
+      <c r="C1" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -878,7 +918,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -889,18 +929,18 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -908,43 +948,43 @@
         <v>2</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -954,11 +994,11 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -969,7 +1009,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -980,7 +1020,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -991,74 +1031,591 @@
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="B17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
+      <c r="B20" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="11"/>
+      <c r="B43" s="1">
+        <f>COUNTIF(B2:B41, "Up")</f>
+        <v>6</v>
+      </c>
+      <c r="C43" s="1">
+        <f>COUNTIF(B2:B41, "Dow")</f>
+        <v>13</v>
+      </c>
+      <c r="D43" s="1">
+        <f>COUNTIF(B2:B41, "Left")</f>
+        <v>13</v>
+      </c>
+      <c r="E43" s="1">
+        <f>COUNTIF(B2:B41, "Right")</f>
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A42:A43"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E34279-DF0B-49D0-978E-1339C67697A9}">
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="C23" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1067,7 +1624,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1076,7 +1633,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1085,7 +1642,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1094,7 +1651,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1103,7 +1660,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1112,7 +1669,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1121,7 +1678,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1130,47 +1687,137 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-      <c r="B33" s="1">
-        <f>COUNTIF(B2:B31, "Up") / COUNTA(A2:A31)</f>
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="C33" s="1">
-        <f>COUNTIF(B1:B100, "Dow") / COUNTA(A2:A31)</f>
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="D33" s="1">
-        <f>COUNTIF(B2:B31, "Left") / COUNTA(A2:A31)</f>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="E33" s="1">
-        <f>COUNTIF(B2:B31, "Right") / COUNTA(A2:A31)</f>
-        <v>6.6666666666666666E-2</v>
+      <c r="B42" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="11"/>
+      <c r="B43" s="1">
+        <f>COUNTIF(B2:B41, "Up")</f>
+        <v>6</v>
+      </c>
+      <c r="C43" s="1">
+        <f>COUNTIF(B2:B41, "Dow")</f>
+        <v>6</v>
+      </c>
+      <c r="D43" s="1">
+        <f>COUNTIF(B2:B41, "Left")</f>
+        <v>7</v>
+      </c>
+      <c r="E43" s="1">
+        <f>COUNTIF(B2:B41, "Right")</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="G13:I13"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A42:A43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
